--- a/quizzes/003_enlightenment_thinkers_quiz--quizzes.xlsx
+++ b/quizzes/003_enlightenment_thinkers_quiz--quizzes.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,7 +520,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>enlightenment_thinkers_quiz_1</t>
+          <t>introduction_page</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>enlightenment_thinkers_quiz_2</t>
+          <t>quiz_question_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Question 1</t>
+          <t>Who is the philosopher known as the "Father of Deism"?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,19 +566,15 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>enlightenment_thinkers_quiz_3</t>
+          <t>quiz_question_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Question 2</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Select multiple options</t>
-        </is>
-      </c>
+          <t>Which philosophical concept is central to the idea of enlightenment?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>yes</t>
@@ -588,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>enlightenment_thinkers_quiz_4</t>
+          <t>quiz_question_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Question 3</t>
+          <t>What is the correct date of the influential book "Discourse on the Method"?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -611,23 +607,23 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>enlightenment_thinkers_quiz_5</t>
+          <t>quiz_question_4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Question 4</t>
+          <t>Which philosopher argued that the universe is governed by natural law and reason?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -639,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>enlightenment_thinkers_quiz_6</t>
+          <t>submission_page</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Question 5</t>
+          <t>Submission</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -662,7 +658,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>enlightenment_thinkers_quiz_7</t>
+          <t>additional_information</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -680,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>enlightenment_thinkers_quiz_8</t>
+          <t>quiz_question_2_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Submission</t>
+          <t>Which thinker's ideas were influential in the development of modern biology?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -708,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>enlightenment_thinkers_quiz_9</t>
+          <t>quiz_question_3_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Submission</t>
+          <t>What type of philosophical approach emphasizes reason over intuition or emotion?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -726,46 +722,46 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>enlightenment_thinkers_quiz_10</t>
+          <t>quiz_question_4_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Submission</t>
+          <t>Which of the following thinkers' ideas emphasized the individual as the center of the universe?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>enlightenment_thinkers_quiz_11</t>
+          <t>quiz_question_5</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Submission</t>
+          <t>Which of the following thinkers believed that the universe was governed by a "clockwork" universe?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -777,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>enlightenment_thinkers_quiz_12</t>
+          <t>submission_page_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Submission</t>
+          <t>Submission Page 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -795,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>enlightenment_thinkers_quiz_13</t>
+          <t>additional_information_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Submission</t>
+          <t>Additional Information 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -823,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>enlightenment_thinkers_quiz_14</t>
+          <t>quiz_question_6</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Submission</t>
+          <t>What is the term for the philosophical and scientific movement of the 17th and 18th century?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -841,23 +837,23 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>enlightenment_thinkers_quiz_15</t>
+          <t>quiz_question_7</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Submission</t>
+          <t>Quiz Question 7</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -869,35 +865,35 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>enlightenment_thinkers_quiz_16</t>
+          <t>submission_page_3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Submission</t>
+          <t>Submission Page 3</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>enlightenment_thinkers_quiz_17</t>
+          <t>additional_information_3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Submission</t>
+          <t>Additional Information 3</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -915,179 +911,18 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>enlightenment_thinkers_quiz_18</t>
+          <t>submission_page_4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Submission</t>
+          <t>Submission Page 4</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>enlightenment_thinkers_quiz_19</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Submission</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>enlightenment_thinkers_quiz_20</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Submission</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>enlightenment_thinkers_quiz_21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Submission</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>enlightenment_thinkers_quiz_22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Submission</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>enlightenment_thinkers_quiz_23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Submission</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>enlightenment_thinkers_quiz_24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Submission</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>enlightenment_thinkers_quiz_25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Submission</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1102,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="39" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1130,7 +965,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>enlightenment_thinkers_quiz_2_choices</t>
+          <t>quiz_question_1_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1147,58 +982,58 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>enlightenment_thinkers_quiz_2_choices</t>
+          <t>quiz_question_1_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>hobbes</t>
+          <t>leibniz</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Hobbes</t>
+          <t>Leibniz</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>enlightenment_thinkers_quiz_2_choices</t>
+          <t>quiz_question_1_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>locke</t>
+          <t>spinoza</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Locke</t>
+          <t>Spinoza</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>enlightenment_thinkers_quiz_2_choices</t>
+          <t>quiz_question_1_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>voltaire</t>
+          <t>descartes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Voltaire</t>
+          <t>Descartes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>enlightenment_thinkers_quiz_3_choices</t>
+          <t>quiz_question_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1215,7 +1050,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>enlightenment_thinkers_quiz_3_choices</t>
+          <t>quiz_question_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1232,7 +1067,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>enlightenment_thinkers_quiz_3_choices</t>
+          <t>quiz_question_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1249,7 +1084,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>enlightenment_thinkers_quiz_3_choices</t>
+          <t>quiz_question_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1260,6 +1095,278 @@
       <c r="C9" t="inlineStr">
         <is>
           <t>Nature</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>quiz_question_4_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>kant</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Kant</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>quiz_question_4_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>hobbes</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Hobbes</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>quiz_question_4_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>descartes</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Descartes</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>quiz_question_4_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>leibniz</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Leibniz</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>quiz_question_2_2_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>rousseau</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Rousseau</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>quiz_question_2_2_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>rousseau_(denis_diderot,_actually_a_follower_of_rousseau's_ideas)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Rousseau (Denis Diderot, actually a follower of Rousseau's ideas)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>quiz_question_4_2_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>rousseau</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Rousseau</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>quiz_question_4_2_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>kant</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Kant</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>quiz_question_5_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>hobbes</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Hobbes</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>quiz_question_5_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>voltaire</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Voltaire</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>quiz_question_5_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>rousseau</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Rousseau</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>quiz_question_5_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>rousseau_(denis_diderot,_actually_a_follower_of_rousseau's_ideas)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Rousseau (Denis Diderot, actually a follower of Rousseau's ideas)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>quiz_question_7_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>hobbes</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Hobbes</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>quiz_question_7_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>voltaire</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Voltaire</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>quiz_question_7_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>rousseau</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Rousseau</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>quiz_question_7_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>rousseau_(denis_diderot,_actually_a_follower_of_rousseau's_ideas)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Rousseau (Denis Diderot, actually a follower of Rousseau's ideas)</t>
         </is>
       </c>
     </row>
